--- a/pembukuan.xlsx
+++ b/pembukuan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\Pengajian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA515592-EBB3-454C-88F6-EAF5D27D3F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40B272D-62E2-4847-870E-0CE557ACC25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="47">
   <si>
     <t>Tanggal</t>
   </si>
@@ -346,8 +346,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D2E55DFE-0EC8-4811-BF5F-68CC494C65C1}" name="Table1_34" displayName="Table1_34" ref="A1:E40" totalsRowShown="0">
-  <autoFilter ref="A1:E40" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D2E55DFE-0EC8-4811-BF5F-68CC494C65C1}" name="Table1_34" displayName="Table1_34" ref="A1:E42" totalsRowShown="0">
+  <autoFilter ref="A1:E42" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8BE68CBF-4C7B-493C-9D2A-190B153DA5AF}" name="Tanggal"/>
     <tableColumn id="2" xr3:uid="{799BA718-157D-4F5F-B22F-0E0734CF2734}" name="Uraian"/>
@@ -2942,16 +2942,34 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="1"/>
+      <c r="A41" s="1">
+        <v>46010</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
       <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="D41" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E41" s="3">
+        <f>E40+Table1_34[[#This Row],[Masuk]]-Table1_34[[#This Row],[Keluar]]</f>
+        <v>6800</v>
+      </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="1"/>
-      <c r="C42" s="3"/>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="3">
+        <v>24000</v>
+      </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="E42" s="3">
+        <f>E41+Table1_34[[#This Row],[Masuk]]-Table1_34[[#This Row],[Keluar]]</f>
+        <v>30800</v>
+      </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="1"/>

--- a/pembukuan.xlsx
+++ b/pembukuan.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\Pengajian\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pengajian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40B272D-62E2-4847-870E-0CE557ACC25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942269E-EE04-4227-A177-0B5D8E5ACA9F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37710" windowHeight="21840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="1" r:id="rId1"/>
     <sheet name="2024" sheetId="2" r:id="rId2"/>
     <sheet name="2025" sheetId="3" r:id="rId3"/>
     <sheet name="2025 (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="April 2026" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -267,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -282,6 +291,7 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2996,4 +3006,17 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB8FC31-11A3-4A12-9538-5E24134D1E27}">
+  <dimension ref="AL56"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="56" spans="38:38">
+      <c r="AL56" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>